--- a/baseline_code/Data/edges_EHAM.xlsx
+++ b/baseline_code/Data/edges_EHAM.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiesa\agent-based-modelling\baseline_code\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20590A24-2D7A-4364-9F8F-4EF30B93DA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -28,8 +34,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -72,26 +77,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -102,10 +107,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -143,71 +148,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -235,7 +240,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -258,11 +263,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -271,13 +276,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -287,7 +292,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -296,7 +301,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -305,7 +310,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -313,10 +318,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -381,19 +386,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C209"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C217"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -404,7 +407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -415,7 +418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>21</v>
       </c>
@@ -426,7 +429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -437,7 +440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>22</v>
       </c>
@@ -448,7 +451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -459,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>35</v>
       </c>
@@ -470,7 +473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -481,7 +484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>36</v>
       </c>
@@ -492,7 +495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>5</v>
       </c>
@@ -503,7 +506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>23</v>
       </c>
@@ -514,7 +517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>6</v>
       </c>
@@ -525,7 +528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>37</v>
       </c>
@@ -536,7 +539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>7</v>
       </c>
@@ -547,7 +550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>26</v>
       </c>
@@ -558,7 +561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>8</v>
       </c>
@@ -569,7 +572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>30</v>
       </c>
@@ -580,7 +583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>9</v>
       </c>
@@ -591,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>28</v>
       </c>
@@ -602,7 +605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>10</v>
       </c>
@@ -613,7 +616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>31</v>
       </c>
@@ -624,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>11</v>
       </c>
@@ -635,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>47</v>
       </c>
@@ -646,7 +649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>12</v>
       </c>
@@ -657,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>48</v>
       </c>
@@ -668,7 +671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>13</v>
       </c>
@@ -679,7 +682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>64</v>
       </c>
@@ -690,7 +693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>14</v>
       </c>
@@ -701,7 +704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>63</v>
       </c>
@@ -712,7 +715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>15</v>
       </c>
@@ -723,7 +726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>73</v>
       </c>
@@ -734,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row r="32" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>16</v>
       </c>
@@ -745,7 +748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row r="33" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>72</v>
       </c>
@@ -756,7 +759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row r="34" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>17</v>
       </c>
@@ -767,7 +770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row r="35" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>71</v>
       </c>
@@ -778,7 +781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row r="36" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>18</v>
       </c>
@@ -789,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>75</v>
       </c>
@@ -800,7 +803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>19</v>
       </c>
@@ -811,7 +814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row r="39" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>70</v>
       </c>
@@ -822,7 +825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row r="40" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>20</v>
       </c>
@@ -833,7 +836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row r="41" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>21</v>
       </c>
@@ -844,7 +847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>20</v>
       </c>
@@ -855,7 +858,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row r="43" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>24</v>
       </c>
@@ -866,7 +869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>21</v>
       </c>
@@ -877,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row r="45" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>22</v>
       </c>
@@ -888,7 +891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row r="46" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>22</v>
       </c>
@@ -899,7 +902,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row r="47" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>23</v>
       </c>
@@ -910,7 +913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row r="48" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>24</v>
       </c>
@@ -921,7 +924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+    <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>25</v>
       </c>
@@ -932,7 +935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+    <row r="50" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>24</v>
       </c>
@@ -943,7 +946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+    <row r="51" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>34</v>
       </c>
@@ -954,7 +957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+    <row r="52" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>25</v>
       </c>
@@ -965,7 +968,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+    <row r="53" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>77</v>
       </c>
@@ -976,7 +979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+    <row r="54" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>25</v>
       </c>
@@ -987,7 +990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+    <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>35</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row r="56" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>26</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row r="57" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>38</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row r="58" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>27</v>
       </c>
@@ -1031,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row r="59" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>28</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row r="60" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>27</v>
       </c>
@@ -1053,7 +1056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row r="61" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>30</v>
       </c>
@@ -1064,7 +1067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row r="62" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>28</v>
       </c>
@@ -1075,7 +1078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row r="63" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>29</v>
       </c>
@@ -1086,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row r="64" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>29</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row r="65" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>31</v>
       </c>
@@ -1108,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row r="66" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>30</v>
       </c>
@@ -1119,7 +1122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row r="67" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>32</v>
       </c>
@@ -1130,7 +1133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row r="68" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>31</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row r="69" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>33</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row r="70" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>32</v>
       </c>
@@ -1163,7 +1166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row r="71" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>33</v>
       </c>
@@ -1174,7 +1177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row r="72" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>32</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row r="73" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>40</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row r="74" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>33</v>
       </c>
@@ -1207,7 +1210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row r="75" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>44</v>
       </c>
@@ -1218,7 +1221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row r="76" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>34</v>
       </c>
@@ -1229,7 +1232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row r="77" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>35</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row r="78" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>34</v>
       </c>
@@ -1251,7 +1254,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row r="79" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>65</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+    <row r="80" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>35</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+    <row r="81" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>36</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+    <row r="82" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>36</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+    <row r="83" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>37</v>
       </c>
@@ -1306,7 +1309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+    <row r="84" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>36</v>
       </c>
@@ -1317,7 +1320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+    <row r="85" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>77</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+    <row r="86" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>37</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+    <row r="87" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>39</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+    <row r="88" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>37</v>
       </c>
@@ -1361,7 +1364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+    <row r="89" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>78</v>
       </c>
@@ -1372,7 +1375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+    <row r="90" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>38</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+    <row r="91" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>41</v>
       </c>
@@ -1394,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+    <row r="92" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>38</v>
       </c>
@@ -1405,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+    <row r="93" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>78</v>
       </c>
@@ -1416,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+    <row r="94" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>39</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+    <row r="95" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>40</v>
       </c>
@@ -1438,7 +1441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+    <row r="96" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>39</v>
       </c>
@@ -1449,7 +1452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+    <row r="97" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>41</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+    <row r="98" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>40</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+    <row r="99" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>44</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+    <row r="100" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>41</v>
       </c>
@@ -1493,7 +1496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+    <row r="101" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>32</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
+    <row r="102" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>44</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
+    <row r="103" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>52</v>
       </c>
@@ -1526,7 +1529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
+    <row r="104" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45</v>
       </c>
@@ -1537,7 +1540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
+    <row r="105" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>46</v>
       </c>
@@ -1548,7 +1551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
+    <row r="106" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45</v>
       </c>
@@ -1559,7 +1562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
+    <row r="107" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>53</v>
       </c>
@@ -1570,7 +1573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
+    <row r="108" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>46</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
+    <row r="109" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>47</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
+    <row r="110" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>47</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
+    <row r="111" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>48</v>
       </c>
@@ -1614,7 +1617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
+    <row r="112" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>48</v>
       </c>
@@ -1625,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
+    <row r="113" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>51</v>
       </c>
@@ -1636,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
+    <row r="114" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>49</v>
       </c>
@@ -1647,7 +1650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
+    <row r="115" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>50</v>
       </c>
@@ -1658,7 +1661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
+    <row r="116" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>49</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
+    <row r="117" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>54</v>
       </c>
@@ -1680,7 +1683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
+    <row r="118" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>50</v>
       </c>
@@ -1691,7 +1694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
+    <row r="119" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>51</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
+    <row r="120" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>52</v>
       </c>
@@ -1713,7 +1716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
+    <row r="121" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>55</v>
       </c>
@@ -1724,7 +1727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
+    <row r="122" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>52</v>
       </c>
@@ -1735,7 +1738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
+    <row r="123" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>53</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
+    <row r="124" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>53</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
+    <row r="125" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>54</v>
       </c>
@@ -1768,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
+    <row r="126" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>53</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
+    <row r="127" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>56</v>
       </c>
@@ -1790,7 +1793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
+    <row r="128" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>54</v>
       </c>
@@ -1801,7 +1804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
+    <row r="129" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>57</v>
       </c>
@@ -1812,7 +1815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
+    <row r="130" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>55</v>
       </c>
@@ -1823,7 +1826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
+    <row r="131" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>56</v>
       </c>
@@ -1834,7 +1837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
+    <row r="132" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>55</v>
       </c>
@@ -1845,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
+    <row r="133" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>69</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
+    <row r="134" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>56</v>
       </c>
@@ -1867,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
+    <row r="135" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>57</v>
       </c>
@@ -1878,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
+    <row r="136" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>56</v>
       </c>
@@ -1889,7 +1892,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
+    <row r="137" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>61</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
+    <row r="138" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>57</v>
       </c>
@@ -1911,7 +1914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
+    <row r="139" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>58</v>
       </c>
@@ -1922,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
+    <row r="140" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>58</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
+    <row r="141" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>59</v>
       </c>
@@ -1944,7 +1947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
+    <row r="142" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>59</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
+    <row r="143" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>60</v>
       </c>
@@ -1966,7 +1969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
+    <row r="144" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>59</v>
       </c>
@@ -1977,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
+    <row r="145" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>62</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
+    <row r="146" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>60</v>
       </c>
@@ -1999,7 +2002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
+    <row r="147" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>64</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
+    <row r="148" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>61</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
+    <row r="149" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>62</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
+    <row r="150" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>62</v>
       </c>
@@ -2043,7 +2046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
+    <row r="151" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>63</v>
       </c>
@@ -2054,7 +2057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
+    <row r="152" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>63</v>
       </c>
@@ -2065,7 +2068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
+    <row r="153" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>64</v>
       </c>
@@ -2076,7 +2079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
+    <row r="154" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>65</v>
       </c>
@@ -2087,7 +2090,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
+    <row r="155" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>66</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
+    <row r="156" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>66</v>
       </c>
@@ -2109,7 +2112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
+    <row r="157" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>67</v>
       </c>
@@ -2120,7 +2123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
+    <row r="158" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>66</v>
       </c>
@@ -2131,7 +2134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
+    <row r="159" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>70</v>
       </c>
@@ -2142,7 +2145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
+    <row r="160" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>67</v>
       </c>
@@ -2153,7 +2156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
+    <row r="161" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>71</v>
       </c>
@@ -2164,7 +2167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
+    <row r="162" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>67</v>
       </c>
@@ -2175,7 +2178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
+    <row r="163" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>68</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
+    <row r="164" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>68</v>
       </c>
@@ -2197,7 +2200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
+    <row r="165" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>72</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
+    <row r="166" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>68</v>
       </c>
@@ -2219,7 +2222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
+    <row r="167" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>82</v>
       </c>
@@ -2230,7 +2233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
+    <row r="168" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>69</v>
       </c>
@@ -2241,7 +2244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
+    <row r="169" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>81</v>
       </c>
@@ -2252,7 +2255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
+    <row r="170" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>70</v>
       </c>
@@ -2263,7 +2266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
+    <row r="171" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>74</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
+    <row r="172" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>71</v>
       </c>
@@ -2285,7 +2288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
+    <row r="173" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>76</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
+    <row r="174" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>72</v>
       </c>
@@ -2307,7 +2310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
+    <row r="175" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>73</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
+    <row r="176" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>74</v>
       </c>
@@ -2329,7 +2332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
+    <row r="177" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>75</v>
       </c>
@@ -2340,7 +2343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
+    <row r="178" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>75</v>
       </c>
@@ -2351,7 +2354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
+    <row r="179" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>76</v>
       </c>
@@ -2362,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+    <row r="180" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>77</v>
       </c>
@@ -2373,7 +2376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
+    <row r="181" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>78</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+    <row r="182" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>79</v>
       </c>
@@ -2395,7 +2398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
+    <row r="183" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>80</v>
       </c>
@@ -2406,7 +2409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
+    <row r="184" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>80</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
+    <row r="185" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>82</v>
       </c>
@@ -2428,7 +2431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
+    <row r="186" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>81</v>
       </c>
@@ -2439,7 +2442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
+    <row r="187" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>82</v>
       </c>
@@ -2450,7 +2453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
+    <row r="188" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>81</v>
       </c>
@@ -2461,7 +2464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
+    <row r="189" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>62</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
+    <row r="190" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>82</v>
       </c>
@@ -2483,7 +2486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
+    <row r="191" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>83</v>
       </c>
@@ -2494,7 +2497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row r="192" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>83</v>
       </c>
@@ -2505,7 +2508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+    <row r="193" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>84</v>
       </c>
@@ -2516,7 +2519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+    <row r="194" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>84</v>
       </c>
@@ -2527,7 +2530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
+    <row r="195" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>85</v>
       </c>
@@ -2538,7 +2541,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row r="196" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>84</v>
       </c>
@@ -2549,7 +2552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
+    <row r="197" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>66</v>
       </c>
@@ -2560,7 +2563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
+    <row r="198" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>83</v>
       </c>
@@ -2571,7 +2574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
+    <row r="199" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>67</v>
       </c>
@@ -2582,7 +2585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
+    <row r="200" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>79</v>
       </c>
@@ -2593,7 +2596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
+    <row r="201" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>52</v>
       </c>
@@ -2604,7 +2607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
+    <row r="202" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>80</v>
       </c>
@@ -2615,7 +2618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
+    <row r="203" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>55</v>
       </c>
@@ -2626,7 +2629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
+    <row r="204" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>68</v>
       </c>
@@ -2637,7 +2640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
+    <row r="205" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>69</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
+    <row r="206" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>69</v>
       </c>
@@ -2659,7 +2662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
+    <row r="207" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>73</v>
       </c>
@@ -2670,7 +2673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
+    <row r="208" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>40</v>
       </c>
@@ -2681,7 +2684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
+    <row r="209" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>79</v>
       </c>
@@ -2690,6 +2693,94 @@
       </c>
       <c r="C209" s="2">
         <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="1">
+        <v>21</v>
+      </c>
+      <c r="B210" s="1">
+        <v>86</v>
+      </c>
+      <c r="C210" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="1">
+        <v>86</v>
+      </c>
+      <c r="B211" s="1">
+        <v>21</v>
+      </c>
+      <c r="C211" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="1">
+        <v>86</v>
+      </c>
+      <c r="B212" s="1">
+        <v>87</v>
+      </c>
+      <c r="C212" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="1">
+        <v>87</v>
+      </c>
+      <c r="B213" s="1">
+        <v>86</v>
+      </c>
+      <c r="C213" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="1">
+        <v>87</v>
+      </c>
+      <c r="B214" s="1">
+        <v>88</v>
+      </c>
+      <c r="C214" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="1">
+        <v>88</v>
+      </c>
+      <c r="B215" s="1">
+        <v>87</v>
+      </c>
+      <c r="C215" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="1">
+        <v>88</v>
+      </c>
+      <c r="B216" s="1">
+        <v>89</v>
+      </c>
+      <c r="C216" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="1">
+        <v>89</v>
+      </c>
+      <c r="B217" s="1">
+        <v>88</v>
+      </c>
+      <c r="C217" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/baseline_code/Data/edges_EHAM.xlsx
+++ b/baseline_code/Data/edges_EHAM.xlsx
@@ -394,7 +394,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -1295,10 +1295,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="1">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B82" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C82" s="1">
         <v>3</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="1">
+        <v>62</v>
+      </c>
+      <c r="B83" s="1">
         <v>61</v>
-      </c>
-      <c r="B83" s="1">
-        <v>81</v>
       </c>
       <c r="C83" s="1">
         <v>3</v>
@@ -1317,164 +1317,164 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B84" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="1">
+        <v>63</v>
+      </c>
+      <c r="B85" s="1">
         <v>62</v>
       </c>
-      <c r="B85" s="1">
-        <v>61</v>
-      </c>
       <c r="C85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B86" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C86" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="1">
+        <v>64</v>
+      </c>
+      <c r="B87" s="1">
         <v>63</v>
       </c>
-      <c r="B87" s="1">
-        <v>62</v>
-      </c>
       <c r="C87" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B88" s="1">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C88" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="1">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="B89" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C89" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="1">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B90" s="1">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="C90" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="1">
+        <v>66</v>
+      </c>
+      <c r="B91" s="1">
         <v>89</v>
       </c>
-      <c r="B91" s="1">
-        <v>65</v>
-      </c>
       <c r="C91" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="1">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="B92" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C92" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="1">
+        <v>67</v>
+      </c>
+      <c r="B93" s="1">
         <v>66</v>
       </c>
-      <c r="B93" s="1">
-        <v>89</v>
-      </c>
       <c r="C93" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B94" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C94" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="1">
+        <v>68</v>
+      </c>
+      <c r="B95" s="1">
         <v>67</v>
       </c>
-      <c r="B95" s="1">
-        <v>66</v>
-      </c>
       <c r="C95" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B96" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C96" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="1">
+        <v>69</v>
+      </c>
+      <c r="B97" s="1">
         <v>68</v>
       </c>
-      <c r="B97" s="1">
-        <v>67</v>
-      </c>
       <c r="C97" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="1">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B98" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C98" s="1">
         <v>2</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B99" s="1">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C99" s="1">
         <v>2</v>
@@ -1493,10 +1493,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="1">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="B100" s="1">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="C100" s="1">
         <v>2</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="1">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B101" s="1">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C101" s="1">
         <v>2</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="1">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="B102" s="1">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C102" s="1">
         <v>2</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="1">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B103" s="1">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C103" s="1">
         <v>2</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="1">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="B104" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C104" s="1">
         <v>2</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="1">
+        <v>73</v>
+      </c>
+      <c r="B105" s="1">
         <v>72</v>
-      </c>
-      <c r="B105" s="1">
-        <v>16</v>
       </c>
       <c r="C105" s="1">
         <v>2</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B106" s="1">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C106" s="1">
         <v>2</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="1">
+        <v>15</v>
+      </c>
+      <c r="B107" s="1">
         <v>73</v>
-      </c>
-      <c r="B107" s="1">
-        <v>72</v>
       </c>
       <c r="C107" s="1">
         <v>2</v>
@@ -1581,32 +1581,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B108" s="1">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="C108" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="1">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B109" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C109" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B110" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C110" s="1">
         <v>1.5</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="1">
+        <v>76</v>
+      </c>
+      <c r="B111" s="1">
         <v>75</v>
-      </c>
-      <c r="B111" s="1">
-        <v>74</v>
       </c>
       <c r="C111" s="1">
         <v>1.5</v>
@@ -1625,32 +1625,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="1">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="B112" s="1">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C112" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="1">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="B113" s="1">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="C113" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B114" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B115" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115" s="1">
         <v>1</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B116" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C116" s="1">
         <v>1</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B117" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C117" s="1">
         <v>1</v>
@@ -1691,76 +1691,76 @@
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="1">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="B118" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C118" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B119" s="1">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="C119" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="1">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="B120" s="1">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="C120" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="1">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B121" s="1">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="C121" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B122" s="1">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C122" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="1">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B123" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C123" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="1">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="B124" s="1">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C124" s="1">
         <v>2</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="1">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B125" s="1">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="C125" s="1">
         <v>2</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="1">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B126" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C126" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B127" s="1">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C127" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="1">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B128" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C128" s="1">
         <v>12</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B129" s="1">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C129" s="1">
         <v>12</v>
@@ -1823,32 +1823,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B130" s="1">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C130" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75">
       <c r="A131" s="1">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="B131" s="1">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C131" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75">
       <c r="A132" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B132" s="1">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C132" s="1">
         <v>2</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75">
       <c r="A133" s="1">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B133" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C133" s="1">
         <v>2</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75">
       <c r="A134" s="1">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="B134" s="1">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="C134" s="1">
         <v>2</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75">
       <c r="A135" s="1">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="B135" s="1">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="C135" s="1">
         <v>2</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75">
       <c r="A136" s="1">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B136" s="1">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C136" s="1">
         <v>2</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75">
       <c r="A137" s="1">
+        <v>3</v>
+      </c>
+      <c r="B137" s="1">
         <v>35</v>
-      </c>
-      <c r="B137" s="1">
-        <v>25</v>
       </c>
       <c r="C137" s="1">
         <v>2</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75">
       <c r="A138" s="1">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="B138" s="1">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C138" s="1">
         <v>2</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75">
       <c r="A139" s="1">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B139" s="1">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C139" s="1">
         <v>2</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75">
       <c r="A140" s="1">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B140" s="1">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="C140" s="1">
         <v>2</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75">
       <c r="A141" s="1">
+        <v>4</v>
+      </c>
+      <c r="B141" s="1">
         <v>36</v>
-      </c>
-      <c r="B141" s="1">
-        <v>77</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75">
       <c r="A142" s="1">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="B142" s="1">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C142" s="1">
         <v>2</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75">
       <c r="A143" s="1">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B143" s="1">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C143" s="1">
         <v>2</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75">
       <c r="A144" s="1">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B144" s="1">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C144" s="1">
         <v>2</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75">
       <c r="A145" s="1">
+        <v>6</v>
+      </c>
+      <c r="B145" s="1">
         <v>37</v>
-      </c>
-      <c r="B145" s="1">
-        <v>78</v>
       </c>
       <c r="C145" s="1">
         <v>2</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75">
       <c r="A146" s="1">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B146" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C146" s="1">
         <v>2</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75">
       <c r="A147" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B147" s="1">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1">
         <v>2</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75">
       <c r="A148" s="1">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B148" s="1">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C148" s="1">
         <v>2</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75">
       <c r="A149" s="1">
+        <v>38</v>
+      </c>
+      <c r="B149" s="1">
         <v>26</v>
-      </c>
-      <c r="B149" s="1">
-        <v>7</v>
       </c>
       <c r="C149" s="1">
         <v>2</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75">
       <c r="A150" s="1">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B150" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C150" s="1">
         <v>2</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75">
       <c r="A151" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B151" s="1">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C151" s="1">
         <v>2</v>
@@ -2065,10 +2065,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75">
       <c r="A152" s="1">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B152" s="1">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C152" s="1">
         <v>2</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75">
       <c r="A153" s="1">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B153" s="1">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C153" s="1">
         <v>2</v>
@@ -2087,32 +2087,32 @@
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75">
       <c r="A154" s="1">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B154" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75">
       <c r="A155" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B155" s="1">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C155" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75">
       <c r="A156" s="1">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B156" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C156" s="1">
         <v>1</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75">
       <c r="A157" s="1">
+        <v>32</v>
+      </c>
+      <c r="B157" s="1">
         <v>30</v>
-      </c>
-      <c r="B157" s="1">
-        <v>27</v>
       </c>
       <c r="C157" s="1">
         <v>1</v>
@@ -2131,164 +2131,164 @@
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75">
       <c r="A158" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B158" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C158" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75">
       <c r="A159" s="1">
+        <v>40</v>
+      </c>
+      <c r="B159" s="1">
         <v>32</v>
       </c>
-      <c r="B159" s="1">
-        <v>30</v>
-      </c>
       <c r="C159" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75">
       <c r="A160" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B160" s="1">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C160" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75">
       <c r="A161" s="1">
+        <v>79</v>
+      </c>
+      <c r="B161" s="1">
         <v>40</v>
       </c>
-      <c r="B161" s="1">
-        <v>32</v>
-      </c>
       <c r="C161" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75">
       <c r="A162" s="1">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B162" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C162" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75">
       <c r="A163" s="1">
+        <v>80</v>
+      </c>
+      <c r="B163" s="1">
         <v>79</v>
       </c>
-      <c r="B163" s="1">
-        <v>40</v>
-      </c>
       <c r="C163" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75">
       <c r="A164" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B164" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C164" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75">
       <c r="A165" s="1">
+        <v>82</v>
+      </c>
+      <c r="B165" s="1">
         <v>80</v>
       </c>
-      <c r="B165" s="1">
-        <v>79</v>
-      </c>
       <c r="C165" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75">
       <c r="A166" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B166" s="1">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C166" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75">
       <c r="A167" s="1">
+        <v>68</v>
+      </c>
+      <c r="B167" s="1">
         <v>82</v>
       </c>
-      <c r="B167" s="1">
-        <v>80</v>
-      </c>
       <c r="C167" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75">
       <c r="A168" s="1">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B168" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C168" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75">
       <c r="A169" s="1">
+        <v>72</v>
+      </c>
+      <c r="B169" s="1">
         <v>68</v>
       </c>
-      <c r="B169" s="1">
-        <v>82</v>
-      </c>
       <c r="C169" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75">
       <c r="A170" s="1">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B170" s="1">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="C170" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75">
       <c r="A171" s="1">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="B171" s="1">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C171" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75">
       <c r="A172" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B172" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C172" s="1">
         <v>1</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75">
       <c r="A173" s="1">
+        <v>33</v>
+      </c>
+      <c r="B173" s="1">
         <v>31</v>
-      </c>
-      <c r="B173" s="1">
-        <v>29</v>
       </c>
       <c r="C173" s="1">
         <v>1</v>
@@ -2307,296 +2307,296 @@
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75">
       <c r="A174" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B174" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C174" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75">
       <c r="A175" s="1">
+        <v>44</v>
+      </c>
+      <c r="B175" s="1">
         <v>33</v>
       </c>
-      <c r="B175" s="1">
-        <v>31</v>
-      </c>
       <c r="C175" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75">
       <c r="A176" s="1">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B176" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C176" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75">
       <c r="A177" s="1">
+        <v>52</v>
+      </c>
+      <c r="B177" s="1">
         <v>44</v>
       </c>
-      <c r="B177" s="1">
-        <v>33</v>
-      </c>
       <c r="C177" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75">
       <c r="A178" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B178" s="1">
+        <v>55</v>
+      </c>
+      <c r="C178" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="19.5">
+      <c r="A179" s="1">
+        <v>55</v>
+      </c>
+      <c r="B179" s="1">
         <v>52</v>
       </c>
-      <c r="C178" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75">
-      <c r="A179" s="1">
-        <v>52</v>
-      </c>
-      <c r="B179" s="1">
-        <v>44</v>
-      </c>
       <c r="C179" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="19.5">
       <c r="A180" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B180" s="1">
+        <v>81</v>
+      </c>
+      <c r="C180" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="19.5">
+      <c r="A181" s="1">
+        <v>81</v>
+      </c>
+      <c r="B181" s="1">
         <v>55</v>
       </c>
-      <c r="C180" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75">
-      <c r="A181" s="1">
-        <v>55</v>
-      </c>
-      <c r="B181" s="1">
-        <v>52</v>
-      </c>
       <c r="C181" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="19.5">
       <c r="A182" s="1">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B182" s="1">
+        <v>69</v>
+      </c>
+      <c r="C182" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="19.5">
+      <c r="A183" s="1">
+        <v>69</v>
+      </c>
+      <c r="B183" s="1">
         <v>81</v>
       </c>
-      <c r="C182" s="1">
+      <c r="C183" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="19.5">
+      <c r="A184" s="1">
+        <v>69</v>
+      </c>
+      <c r="B184" s="1">
+        <v>73</v>
+      </c>
+      <c r="C184" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="19.5">
+      <c r="A185" s="1">
+        <v>73</v>
+      </c>
+      <c r="B185" s="1">
+        <v>69</v>
+      </c>
+      <c r="C185" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="19.5">
+      <c r="A186" s="1">
+        <v>45</v>
+      </c>
+      <c r="B186" s="1">
+        <v>53</v>
+      </c>
+      <c r="C186" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75">
-      <c r="A183" s="1">
-        <v>81</v>
-      </c>
-      <c r="B183" s="1">
-        <v>55</v>
-      </c>
-      <c r="C183" s="1">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="19.5">
+      <c r="A187" s="1">
+        <v>53</v>
+      </c>
+      <c r="B187" s="1">
+        <v>45</v>
+      </c>
+      <c r="C187" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75">
-      <c r="A184" s="1">
-        <v>81</v>
-      </c>
-      <c r="B184" s="1">
-        <v>69</v>
-      </c>
-      <c r="C184" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75">
-      <c r="A185" s="1">
-        <v>69</v>
-      </c>
-      <c r="B185" s="1">
-        <v>81</v>
-      </c>
-      <c r="C185" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75">
-      <c r="A186" s="1">
-        <v>69</v>
-      </c>
-      <c r="B186" s="1">
-        <v>73</v>
-      </c>
-      <c r="C186" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75">
-      <c r="A187" s="1">
-        <v>73</v>
-      </c>
-      <c r="B187" s="1">
-        <v>69</v>
-      </c>
-      <c r="C187" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="19.5">
       <c r="A188" s="1">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B188" s="1">
+        <v>56</v>
+      </c>
+      <c r="C188" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="19.5">
+      <c r="A189" s="1">
+        <v>56</v>
+      </c>
+      <c r="B189" s="1">
         <v>53</v>
       </c>
-      <c r="C188" s="1">
+      <c r="C189" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="19.5">
+      <c r="A190" s="1">
+        <v>56</v>
+      </c>
+      <c r="B190" s="1">
+        <v>61</v>
+      </c>
+      <c r="C190" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75">
-      <c r="A189" s="1">
-        <v>53</v>
-      </c>
-      <c r="B189" s="1">
-        <v>45</v>
-      </c>
-      <c r="C189" s="1">
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="19.5">
+      <c r="A191" s="1">
+        <v>61</v>
+      </c>
+      <c r="B191" s="1">
+        <v>56</v>
+      </c>
+      <c r="C191" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75">
-      <c r="A190" s="1">
-        <v>53</v>
-      </c>
-      <c r="B190" s="1">
-        <v>56</v>
-      </c>
-      <c r="C190" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75">
-      <c r="A191" s="1">
-        <v>56</v>
-      </c>
-      <c r="B191" s="1">
-        <v>53</v>
-      </c>
-      <c r="C191" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="19.5">
       <c r="A192" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B192" s="1">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C192" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="19.5">
       <c r="A193" s="1">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B193" s="1">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C193" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="19.5">
       <c r="A194" s="1">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B194" s="1">
+        <v>57</v>
+      </c>
+      <c r="C194" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="19.5">
+      <c r="A195" s="1">
+        <v>57</v>
+      </c>
+      <c r="B195" s="1">
         <v>54</v>
       </c>
-      <c r="C194" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75">
-      <c r="A195" s="1">
-        <v>54</v>
-      </c>
-      <c r="B195" s="1">
-        <v>49</v>
-      </c>
       <c r="C195" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="19.5">
       <c r="A196" s="1">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B196" s="1">
+        <v>58</v>
+      </c>
+      <c r="C196" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="19.5">
+      <c r="A197" s="1">
+        <v>58</v>
+      </c>
+      <c r="B197" s="1">
         <v>57</v>
       </c>
-      <c r="C196" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75">
-      <c r="A197" s="1">
-        <v>57</v>
-      </c>
-      <c r="B197" s="1">
-        <v>54</v>
-      </c>
       <c r="C197" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="19.5">
       <c r="A198" s="1">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B198" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C198" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="19.5">
       <c r="A199" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B199" s="1">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C199" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75">
       <c r="A200" s="1">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B200" s="1">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C200" s="1">
         <v>1</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75">
       <c r="A201" s="1">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B201" s="1">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C201" s="1">
         <v>1</v>
@@ -2615,208 +2615,208 @@
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75">
       <c r="A202" s="1">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B202" s="1">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C202" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75">
       <c r="A203" s="1">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B203" s="1">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C203" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75">
       <c r="A204" s="1">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B204" s="1">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C204" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75">
       <c r="A205" s="1">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B205" s="1">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C205" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
       <c r="A206" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B206" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C206" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
       <c r="A207" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B207" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C207" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
       <c r="A208" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B208" s="1">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C208" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
       <c r="A209" s="1">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B209" s="1">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C209" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
       <c r="A210" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B210" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C210" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
       <c r="A211" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B211" s="1">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C211" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
       <c r="A212" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B212" s="1">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C212" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
       <c r="A213" s="1">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B213" s="1">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C213" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
       <c r="A214" s="1">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B214" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C214" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
       <c r="A215" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B215" s="1">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C215" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
       <c r="A216" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B216" s="1">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C216" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
       <c r="A217" s="1">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B217" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C217" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
-      <c r="A218" s="2">
-        <v>64</v>
-      </c>
-      <c r="B218" s="2">
-        <v>13</v>
-      </c>
-      <c r="C218" s="2">
-        <v>2</v>
+      <c r="A218" s="1">
+        <v>70</v>
+      </c>
+      <c r="B218" s="1">
+        <v>74</v>
+      </c>
+      <c r="C218" s="1">
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
-      <c r="A219" s="1">
-        <v>13</v>
-      </c>
-      <c r="B219" s="1">
-        <v>64</v>
-      </c>
-      <c r="C219" s="1">
-        <v>2</v>
+      <c r="A219" s="2">
+        <v>74</v>
+      </c>
+      <c r="B219" s="2">
+        <v>70</v>
+      </c>
+      <c r="C219" s="2">
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
       <c r="A220" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B220" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C220" s="2">
         <v>2</v>
@@ -2824,10 +2824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
       <c r="A221" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B221" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C221" s="2">
         <v>2</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
       <c r="A222" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B222" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C222" s="2">
         <v>4</v>
@@ -2846,144 +2846,278 @@
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
       <c r="A223" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B223" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C223" s="2">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
-      <c r="A224" s="2">
-        <v>70</v>
-      </c>
-      <c r="B224" s="2">
-        <v>74</v>
-      </c>
-      <c r="C224" s="2">
+      <c r="A224" s="1">
+        <v>71</v>
+      </c>
+      <c r="B224" s="1">
+        <v>76</v>
+      </c>
+      <c r="C224" s="1">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
-      <c r="A225" s="3">
-        <v>74</v>
-      </c>
-      <c r="B225" s="3">
-        <v>70</v>
-      </c>
-      <c r="C225" s="3">
+      <c r="A225" s="2">
+        <v>76</v>
+      </c>
+      <c r="B225" s="2">
+        <v>71</v>
+      </c>
+      <c r="C225" s="2">
         <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="17.25">
-      <c r="A226" s="3">
-        <v>83</v>
-      </c>
-      <c r="B226" s="3">
-        <v>67</v>
-      </c>
-      <c r="C226" s="3">
+      <c r="A226" s="2">
+        <v>75</v>
+      </c>
+      <c r="B226" s="2">
+        <v>18</v>
+      </c>
+      <c r="C226" s="2">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="17.25">
-      <c r="A227" s="3">
-        <v>67</v>
-      </c>
-      <c r="B227" s="3">
-        <v>83</v>
-      </c>
-      <c r="C227" s="3">
+      <c r="A227" s="1">
+        <v>18</v>
+      </c>
+      <c r="B227" s="1">
+        <v>75</v>
+      </c>
+      <c r="C227" s="1">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="17.25">
-      <c r="A228" s="3">
-        <v>67</v>
-      </c>
-      <c r="B228" s="3">
-        <v>71</v>
-      </c>
-      <c r="C228" s="3">
-        <v>4</v>
+      <c r="A228" s="2">
+        <v>20</v>
+      </c>
+      <c r="B228" s="2">
+        <v>90</v>
+      </c>
+      <c r="C228" s="2">
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="17.25">
-      <c r="A229" s="3">
-        <v>71</v>
-      </c>
-      <c r="B229" s="3">
-        <v>67</v>
-      </c>
-      <c r="C229" s="3">
-        <v>4</v>
+      <c r="A229" s="2">
+        <v>90</v>
+      </c>
+      <c r="B229" s="2">
+        <v>20</v>
+      </c>
+      <c r="C229" s="2">
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="17.25">
       <c r="A230" s="2">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="B230" s="2">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C230" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="17.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75">
       <c r="A231" s="3">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="B231" s="3">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="C231" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
-      <c r="A232" s="3">
-        <v>75</v>
-      </c>
-      <c r="B232" s="3">
-        <v>18</v>
-      </c>
-      <c r="C232" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="17.25">
-      <c r="A233" s="2">
-        <v>18</v>
-      </c>
-      <c r="B233" s="2">
-        <v>75</v>
-      </c>
-      <c r="C233" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3"/>
-      <c r="C234" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="17.25">
-      <c r="A235" s="3"/>
-      <c r="B235" s="3"/>
-      <c r="C235" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="17.25">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3"/>
-      <c r="C236" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
-      <c r="A237" s="3"/>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75">
+      <c r="A232" s="2">
+        <v>90</v>
+      </c>
+      <c r="B232" s="2">
+        <v>91</v>
+      </c>
+      <c r="C232" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75">
+      <c r="A233" s="3">
+        <v>91</v>
+      </c>
+      <c r="B233" s="3">
+        <v>90</v>
+      </c>
+      <c r="C233" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75">
+      <c r="A234" s="3">
+        <v>91</v>
+      </c>
+      <c r="B234" s="3">
+        <v>92</v>
+      </c>
+      <c r="C234" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75">
+      <c r="A235" s="3">
+        <v>92</v>
+      </c>
+      <c r="B235" s="3">
+        <v>91</v>
+      </c>
+      <c r="C235" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75">
+      <c r="A236" s="3">
+        <v>92</v>
+      </c>
+      <c r="B236" s="3">
+        <v>93</v>
+      </c>
+      <c r="C236" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75">
+      <c r="A237" s="3">
+        <v>93</v>
+      </c>
+      <c r="B237" s="3">
+        <v>92</v>
+      </c>
+      <c r="C237" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75">
+      <c r="A238" s="3">
+        <v>92</v>
+      </c>
+      <c r="B238" s="3">
+        <v>22</v>
+      </c>
+      <c r="C238" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75">
+      <c r="A239" s="3">
+        <v>22</v>
+      </c>
+      <c r="B239" s="3">
+        <v>92</v>
+      </c>
+      <c r="C239" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75">
+      <c r="A240" s="3">
+        <v>23</v>
+      </c>
+      <c r="B240" s="3">
+        <v>93</v>
+      </c>
+      <c r="C240" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75">
+      <c r="A241" s="3">
+        <v>93</v>
+      </c>
+      <c r="B241" s="3">
+        <v>23</v>
+      </c>
+      <c r="C241" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75">
+      <c r="A242" s="3">
+        <v>90</v>
+      </c>
+      <c r="B242" s="3">
+        <v>94</v>
+      </c>
+      <c r="C242" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75">
+      <c r="A243" s="3">
+        <v>94</v>
+      </c>
+      <c r="B243" s="3">
+        <v>90</v>
+      </c>
+      <c r="C243" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75">
+      <c r="A244" s="3">
+        <v>91</v>
+      </c>
+      <c r="B244" s="3">
+        <v>95</v>
+      </c>
+      <c r="C244" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75">
+      <c r="A245" s="3">
+        <v>95</v>
+      </c>
+      <c r="B245" s="3">
+        <v>91</v>
+      </c>
+      <c r="C245" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75">
+      <c r="A246" s="3">
+        <v>94</v>
+      </c>
+      <c r="B246" s="3">
+        <v>95</v>
+      </c>
+      <c r="C246" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="17.25">
+      <c r="A247" s="3">
+        <v>95</v>
+      </c>
+      <c r="B247" s="3">
+        <v>94</v>
+      </c>
+      <c r="C247" s="3">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
